--- a/public/assets/files/SampleLeadsnew.xlsx
+++ b/public/assets/files/SampleLeadsnew.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t xml:space="preserve">Full Name</t>
   </si>
@@ -57,10 +57,10 @@
     <t xml:space="preserve">Child Service</t>
   </si>
   <si>
-    <t xml:space="preserve">dev11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dev1@mail.commm</t>
+    <t xml:space="preserve">Patient1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient@mail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Male</t>
@@ -78,64 +78,31 @@
     <t xml:space="preserve">Body Contouring</t>
   </si>
   <si>
-    <t xml:space="preserve">CUTERA, DHA Karachi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULTIMATE - Cool Sculpting (large)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dev22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dev2@mail.commm</t>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cutera SCULPT - Single probe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUTERA, Johar Town, Lahore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female</t>
   </si>
   <si>
     <t xml:space="preserve">Karachi</t>
   </si>
   <si>
-    <t xml:space="preserve">Skin Treatments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUTERA, Bahadurabad Karachi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4D - HIFU Bingo Wings1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dev33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dev3@mail.commm</t>
+    <t xml:space="preserve">Islamabad</t>
   </si>
   <si>
     <t xml:space="preserve">Peshawar</t>
   </si>
   <si>
     <t xml:space="preserve">Social Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUTERA, Johar Town, Lahore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dev44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dev4@mail.commm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Islamabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laser Hair Removal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUTERA, Gulshan/Johar Karachi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoolGlide - Beard line Hair removal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female</t>
   </si>
   <si>
     <t xml:space="preserve">Referral</t>
@@ -169,7 +136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -191,20 +158,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="11"/>
-      <color rgb="FF0563C1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -232,7 +185,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
+  <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -256,16 +209,13 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -273,92 +223,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0563C1"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -373,6 +250,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="29.77"/>
@@ -414,13 +292,13 @@
       <c r="A2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>20131130100</v>
-      </c>
-      <c r="D2" s="0" t="s">
+        <v>12345678</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="0" t="s">
@@ -438,7 +316,7 @@
       <c r="I2" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -446,104 +324,40 @@
       <c r="A3" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
+      <c r="B3" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>20141141001</v>
-      </c>
-      <c r="D3" s="0" t="s">
+        <v>87654321</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>23</v>
+      <c r="H3" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>20141150142</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>20111061003</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>35</v>
-      </c>
-    </row>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="dev1@mail.commm"/>
-    <hyperlink ref="B3" r:id="rId2" display="dev2@mail.commm"/>
-    <hyperlink ref="B4" r:id="rId3" display="dev3@mail.commm"/>
-    <hyperlink ref="B5" r:id="rId4" display="dev4@mail.commm"/>
+    <hyperlink ref="B2" r:id="rId1" display="Patient@mail.com"/>
+    <hyperlink ref="B3" r:id="rId2" display="Patient@mail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -564,7 +378,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -575,7 +389,7 @@
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -598,7 +412,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -609,17 +423,17 @@
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -642,7 +456,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -653,17 +467,17 @@
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -686,7 +500,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -697,22 +511,22 @@
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -735,18 +549,18 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/files/SampleLeadsnew.xlsx
+++ b/public/assets/files/SampleLeadsnew.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t xml:space="preserve">Full Name</t>
   </si>
@@ -48,16 +48,16 @@
     <t xml:space="preserve">Lead Status</t>
   </si>
   <si>
+    <t xml:space="preserve">Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centre</t>
+  </si>
+  <si>
     <t xml:space="preserve">Treatment</t>
   </si>
   <si>
-    <t xml:space="preserve">Centre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Child Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient1</t>
+    <t xml:space="preserve">Patient13</t>
   </si>
   <si>
     <t xml:space="preserve">Patient@mail.com</t>
@@ -78,16 +78,13 @@
     <t xml:space="preserve">Body Contouring</t>
   </si>
   <si>
-    <t xml:space="preserve">N/A</t>
+    <t xml:space="preserve">CUTERA, Johar Town, Lahore</t>
   </si>
   <si>
     <t xml:space="preserve">Cutera SCULPT - Single probe</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUTERA, Johar Town, Lahore</t>
+    <t xml:space="preserve">Patient24</t>
   </si>
   <si>
     <t xml:space="preserve">Female</t>
@@ -215,16 +212,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -244,7 +241,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.28"/>
@@ -256,35 +253,35 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="29.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -296,9 +293,9 @@
         <v>11</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>12345678</v>
-      </c>
-      <c r="D2" s="1" t="s">
+        <v>8105206747</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="0" t="s">
@@ -310,13 +307,13 @@
       <c r="G2" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -328,9 +325,9 @@
         <v>11</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>87654321</v>
-      </c>
-      <c r="D3" s="1" t="s">
+        <v>930313247</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="0" t="s">
@@ -343,17 +340,18 @@
         <v>15</v>
       </c>
       <c r="H3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>17</v>
+      <c r="J3" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="Patient@mail.com"/>
@@ -378,7 +376,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -389,7 +387,7 @@
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -412,7 +410,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -423,17 +421,17 @@
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -456,7 +454,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -467,17 +465,17 @@
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -500,7 +498,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -511,22 +509,22 @@
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -549,18 +547,18 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>7</v>
+      <c r="A1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
